--- a/artfynd/A 5166-2026 artfynd.xlsx
+++ b/artfynd/A 5166-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129840235</v>
       </c>
       <c r="B3" t="n">
-        <v>58117</v>
+        <v>58124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5166-2026 artfynd.xlsx
+++ b/artfynd/A 5166-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129840235</v>
       </c>
       <c r="B3" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5166-2026 artfynd.xlsx
+++ b/artfynd/A 5166-2026 artfynd.xlsx
@@ -675,58 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88609289</v>
+        <v>129840235</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöbo, Sk</t>
+          <t>Stora Altona, Stora Altona, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424021.0306906863</v>
+        <v>423665</v>
       </c>
       <c r="R2" t="n">
-        <v>6162710.74696087</v>
+        <v>6162770</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,64 +774,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexandra Adriani</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexandra Adriani</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129840235</v>
+        <v>88609287</v>
       </c>
       <c r="B3" t="n">
-        <v>58134</v>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Altona, Stora Altona, Sk</t>
+          <t>Sjöbo, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423665</v>
+        <v>424021</v>
       </c>
       <c r="R3" t="n">
-        <v>6162770</v>
+        <v>6162711</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2020-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2020-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +886,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Alexandra Adriani</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Alexandra Adriani</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
